--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N58_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>8.249597095335714</v>
       </c>
       <c r="E2" t="n">
-        <v>4.865766466646718</v>
+        <v>4.307908328169757</v>
       </c>
       <c r="F2" t="n">
-        <v>1.343033127672012</v>
+        <v>1.976664988249474</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>8.211237039224068</v>
       </c>
       <c r="E3" t="n">
-        <v>4.865766466646718</v>
+        <v>4.307908328169757</v>
       </c>
       <c r="F3" t="n">
-        <v>1.343033127672012</v>
+        <v>1.976664988249474</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,23 +544,55 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
+        <v>4.857009329548625</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.489021562186323</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.307908328169757</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.976664988249474</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>T7604</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W0029F0003T0006Z000C1N58.png</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
         <v>12.81234910582835</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>11.07922687115965</v>
       </c>
-      <c r="E4" t="n">
-        <v>4.865766466646718</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.343033127672012</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="E5" t="n">
+        <v>4.307908328169757</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.976664988249474</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>T7604</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.064356997087023</v>
+        <v>1.147958012026641</v>
       </c>
       <c r="D2" t="n">
-        <v>8.249597095335714</v>
+        <v>1.340559527992054</v>
       </c>
       <c r="E2" t="n">
-        <v>4.307908328169757</v>
+        <v>0.7000351033275856</v>
       </c>
       <c r="F2" t="n">
-        <v>1.976664988249474</v>
+        <v>0.3212080605905394</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8961732852656761</v>
+        <v>0.1456281588556724</v>
       </c>
       <c r="D3" t="n">
-        <v>8.211237039224068</v>
+        <v>1.334326018873911</v>
       </c>
       <c r="E3" t="n">
-        <v>4.307908328169757</v>
+        <v>0.7000351033275856</v>
       </c>
       <c r="F3" t="n">
-        <v>1.976664988249474</v>
+        <v>0.3212080605905394</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4.857009329548625</v>
+        <v>0.7892640160516516</v>
       </c>
       <c r="D4" t="n">
-        <v>5.489021562186323</v>
+        <v>0.8919660038552776</v>
       </c>
       <c r="E4" t="n">
-        <v>4.307908328169757</v>
+        <v>0.7000351033275856</v>
       </c>
       <c r="F4" t="n">
-        <v>1.976664988249474</v>
+        <v>0.3212080605905394</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.81234910582835</v>
+        <v>2.082006729697107</v>
       </c>
       <c r="D5" t="n">
-        <v>11.07922687115965</v>
+        <v>1.800374366563443</v>
       </c>
       <c r="E5" t="n">
-        <v>4.307908328169757</v>
+        <v>0.7000351033275856</v>
       </c>
       <c r="F5" t="n">
-        <v>1.976664988249474</v>
+        <v>0.3212080605905394</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
